--- a/分析结果.xlsx
+++ b/分析结果.xlsx
@@ -448,7 +448,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.375</v>
+        <v>-0.227</v>
       </c>
     </row>
     <row r="3">
@@ -461,7 +461,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.67</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="4">
@@ -474,7 +474,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.697</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.667</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="6">
@@ -513,7 +513,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +526,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>0.61</v>
+        <v>0.538</v>
       </c>
     </row>
   </sheetData>
@@ -587,25 +587,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -615,25 +615,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="C3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D3" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="E3" t="n">
-        <v>4.88</v>
+        <v>4.92</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="H3" t="n">
-        <v>4.79</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="4">
@@ -643,25 +643,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="C4" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="D4" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="G4" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="H4" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="5">
@@ -699,25 +699,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="C6" t="n">
-        <v>4.65</v>
+        <v>4.85</v>
       </c>
       <c r="D6" t="n">
-        <v>3.19</v>
+        <v>2.56</v>
       </c>
       <c r="E6" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H6" t="n">
         <v>4.75</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.58</v>
       </c>
     </row>
     <row r="7">
@@ -730,7 +730,7 @@
         <v>4.5</v>
       </c>
       <c r="C7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>3.5</v>
@@ -745,7 +745,7 @@
         <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="C8" t="n">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="D8" t="n">
-        <v>3.56</v>
+        <v>3.69</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="G8" t="n">
-        <v>4.62</v>
+        <v>4.88</v>
       </c>
       <c r="H8" t="n">
-        <v>5.04</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="9">
@@ -979,25 +979,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="C2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D2" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="E2" t="n">
-        <v>4.88</v>
+        <v>4.92</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="H2" t="n">
-        <v>4.79</v>
+        <v>4.89</v>
       </c>
     </row>
   </sheetData>
@@ -1091,25 +1091,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.47</v>
+        <v>4.52</v>
       </c>
       <c r="C3" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H3" t="n">
         <v>5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.94</v>
       </c>
     </row>
   </sheetData>
@@ -1173,22 +1173,22 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.12</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.763</v>
+        <v>-0.842</v>
       </c>
       <c r="E2" t="n">
-        <v>0.775</v>
+        <v>0.674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.316</v>
+        <v>0.512</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.316</v>
+        <v>-0.366</v>
       </c>
       <c r="H2" t="n">
-        <v>0.291</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="3">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.12</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.171</v>
+        <v>-0.074</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.131</v>
       </c>
       <c r="F3" t="n">
-        <v>0.756</v>
+        <v>0.639</v>
       </c>
       <c r="G3" t="n">
-        <v>0.945</v>
+        <v>0.923</v>
       </c>
       <c r="H3" t="n">
-        <v>0.905</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="4">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.763</v>
+        <v>-0.842</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.171</v>
+        <v>-0.074</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.246</v>
+        <v>-0.227</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.754</v>
+        <v>-0.801</v>
       </c>
       <c r="G4" t="n">
-        <v>0.151</v>
+        <v>0.308</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.555</v>
+        <v>-0.542</v>
       </c>
     </row>
     <row r="5">
@@ -1254,25 +1254,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.775</v>
+        <v>0.674</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.131</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.246</v>
+        <v>-0.227</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="H5" t="n">
-        <v>0.225</v>
+        <v>0.332</v>
       </c>
     </row>
     <row r="6">
@@ -1282,25 +1282,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.316</v>
+        <v>0.512</v>
       </c>
       <c r="C6" t="n">
-        <v>0.756</v>
+        <v>0.639</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.754</v>
+        <v>-0.801</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.294</v>
       </c>
       <c r="H6" t="n">
-        <v>0.921</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="7">
@@ -1310,25 +1310,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.316</v>
+        <v>-0.366</v>
       </c>
       <c r="C7" t="n">
-        <v>0.945</v>
+        <v>0.923</v>
       </c>
       <c r="D7" t="n">
-        <v>0.151</v>
+        <v>0.308</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0.294</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.736</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="8">
@@ -1338,22 +1338,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.291</v>
+        <v>0.392</v>
       </c>
       <c r="C8" t="n">
-        <v>0.905</v>
+        <v>0.87</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.555</v>
+        <v>-0.542</v>
       </c>
       <c r="E8" t="n">
-        <v>0.225</v>
+        <v>0.332</v>
       </c>
       <c r="F8" t="n">
-        <v>0.921</v>
+        <v>0.901</v>
       </c>
       <c r="G8" t="n">
-        <v>0.736</v>
+        <v>0.631</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>

--- a/分析结果.xlsx
+++ b/分析结果.xlsx
@@ -448,7 +448,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.227</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -461,7 +461,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.595</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="4">
@@ -474,7 +474,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.742</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>-4.8</v>
+        <v>-1.385</v>
       </c>
     </row>
     <row r="6">
@@ -500,7 +500,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="7">
@@ -513,7 +513,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.471</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +526,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>0.538</v>
+        <v>0.5590000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -587,25 +587,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -615,25 +615,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.53</v>
+        <v>4.34</v>
       </c>
       <c r="C3" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="D3" t="n">
-        <v>3.17</v>
+        <v>3.75</v>
       </c>
       <c r="E3" t="n">
-        <v>4.92</v>
+        <v>4.79</v>
       </c>
       <c r="F3" t="n">
-        <v>5.17</v>
+        <v>4.5</v>
       </c>
       <c r="G3" t="n">
-        <v>4.58</v>
+        <v>4.43</v>
       </c>
       <c r="H3" t="n">
-        <v>4.89</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="4">
@@ -643,25 +643,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.24</v>
+        <v>0.75</v>
       </c>
       <c r="C4" t="n">
-        <v>0.37</v>
+        <v>0.49</v>
       </c>
       <c r="D4" t="n">
-        <v>0.72</v>
+        <v>1.12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.39</v>
       </c>
       <c r="F4" t="n">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="G4" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="H4" t="n">
-        <v>0.33</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="5">
@@ -671,25 +671,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="D5" t="n">
         <v>2.25</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>4.33</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="6">
@@ -699,25 +699,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="C6" t="n">
-        <v>4.85</v>
+        <v>4.3</v>
       </c>
       <c r="D6" t="n">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="G6" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="D7" t="n">
         <v>3.5</v>
@@ -739,13 +739,13 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G7" t="n">
         <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="8">
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.15</v>
+        <v>4.9</v>
       </c>
       <c r="D8" t="n">
-        <v>3.69</v>
+        <v>3.75</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>4.88</v>
+        <v>4.75</v>
       </c>
       <c r="H8" t="n">
-        <v>5.12</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="9">
@@ -783,13 +783,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="C9" t="n">
         <v>5.2</v>
       </c>
       <c r="D9" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>5</v>
@@ -867,22 +867,22 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C2" t="n">
         <v>4.4</v>
       </c>
-      <c r="C2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="D2" t="n">
-        <v>3.5</v>
+        <v>4.12</v>
       </c>
       <c r="E2" t="n">
-        <v>4.75</v>
+        <v>4.88</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="G2" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="H2" t="n">
         <v>4.5</v>
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="C3" t="n">
-        <v>5.1</v>
+        <v>4.87</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="F3" t="n">
-        <v>5.5</v>
+        <v>4.83</v>
       </c>
       <c r="G3" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="H3" t="n">
-        <v>5.08</v>
+        <v>4.67</v>
       </c>
     </row>
   </sheetData>
@@ -979,25 +979,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.53</v>
+        <v>4.34</v>
       </c>
       <c r="C2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="D2" t="n">
-        <v>3.17</v>
+        <v>3.75</v>
       </c>
       <c r="E2" t="n">
-        <v>4.92</v>
+        <v>4.79</v>
       </c>
       <c r="F2" t="n">
-        <v>5.17</v>
+        <v>4.5</v>
       </c>
       <c r="G2" t="n">
-        <v>4.58</v>
+        <v>4.43</v>
       </c>
       <c r="H2" t="n">
-        <v>4.89</v>
+        <v>4.57</v>
       </c>
     </row>
   </sheetData>
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="C2" t="n">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="H2" t="n">
         <v>4.33</v>
@@ -1091,25 +1091,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.52</v>
+        <v>4.1</v>
       </c>
       <c r="C3" t="n">
-        <v>5.04</v>
+        <v>4.95</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1</v>
+        <v>3.88</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9</v>
+        <v>4.88</v>
       </c>
       <c r="F3" t="n">
-        <v>5.4</v>
+        <v>4.88</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
     </row>
   </sheetData>
@@ -1173,22 +1173,22 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.438</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.842</v>
+        <v>-0.8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.674</v>
+        <v>0.235</v>
       </c>
       <c r="F2" t="n">
-        <v>0.512</v>
+        <v>0.539</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.366</v>
+        <v>0.632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.392</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="3">
@@ -1198,25 +1198,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.438</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.074</v>
+        <v>0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>0.131</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.639</v>
+        <v>0.447</v>
       </c>
       <c r="G3" t="n">
-        <v>0.923</v>
+        <v>0.076</v>
       </c>
       <c r="H3" t="n">
-        <v>0.87</v>
+        <v>0.331</v>
       </c>
     </row>
     <row r="4">
@@ -1226,25 +1226,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.842</v>
+        <v>-0.8</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.074</v>
+        <v>0.03</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.227</v>
+        <v>0.047</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.801</v>
+        <v>-0.735</v>
       </c>
       <c r="G4" t="n">
-        <v>0.308</v>
+        <v>-0.373</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.542</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="5">
@@ -1254,25 +1254,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.674</v>
+        <v>0.235</v>
       </c>
       <c r="C5" t="n">
-        <v>0.131</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.227</v>
+        <v>0.047</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.108</v>
+        <v>0.348</v>
       </c>
       <c r="G5" t="n">
-        <v>0.108</v>
+        <v>0.37</v>
       </c>
       <c r="H5" t="n">
-        <v>0.332</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="6">
@@ -1282,25 +1282,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.512</v>
+        <v>0.539</v>
       </c>
       <c r="C6" t="n">
-        <v>0.639</v>
+        <v>0.447</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.801</v>
+        <v>-0.735</v>
       </c>
       <c r="E6" t="n">
-        <v>0.108</v>
+        <v>0.348</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.294</v>
+        <v>0.609</v>
       </c>
       <c r="H6" t="n">
-        <v>0.901</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="7">
@@ -1310,25 +1310,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.366</v>
+        <v>0.632</v>
       </c>
       <c r="C7" t="n">
-        <v>0.923</v>
+        <v>0.076</v>
       </c>
       <c r="D7" t="n">
-        <v>0.308</v>
+        <v>-0.373</v>
       </c>
       <c r="E7" t="n">
-        <v>0.108</v>
+        <v>0.37</v>
       </c>
       <c r="F7" t="n">
-        <v>0.294</v>
+        <v>0.609</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.631</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -1338,22 +1338,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.392</v>
+        <v>0.603</v>
       </c>
       <c r="C8" t="n">
-        <v>0.87</v>
+        <v>0.331</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.542</v>
+        <v>-0.57</v>
       </c>
       <c r="E8" t="n">
-        <v>0.332</v>
+        <v>0.61</v>
       </c>
       <c r="F8" t="n">
-        <v>0.901</v>
+        <v>0.92</v>
       </c>
       <c r="G8" t="n">
-        <v>0.631</v>
+        <v>0.8</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
